--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92501</v>
+        <v>92511</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83492</v>
+        <v>83502</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>137287302</v>
       </c>
       <c r="B45" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,6 +5310,10 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skog mellan Blattniksklimpen och Stålfjäll, Ly lm</t>
@@ -5391,7 +5395,7 @@
         <v>137287284</v>
       </c>
       <c r="B46" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5417,6 +5421,10 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skog mellan Blattniksklimpen och Stålfjäll, Ly lm</t>
@@ -5498,7 +5506,7 @@
         <v>137287304</v>
       </c>
       <c r="B47" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5712,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5819,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5926,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6033,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6140,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6354,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6461,7 +6469,7 @@
         <v>137287258</v>
       </c>
       <c r="B56" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,6 +6495,10 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skog mellan Blattniksklimpen och Stålfjäll, Ly lm</t>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92511</v>
+        <v>92512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92512</v>
+        <v>92515</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>137287302</v>
       </c>
       <c r="B45" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137287284</v>
       </c>
       <c r="B46" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89384</v>
+        <v>89387</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>137287258</v>
       </c>
       <c r="B56" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92515</v>
+        <v>92517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>137287302</v>
       </c>
       <c r="B45" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137287284</v>
       </c>
       <c r="B46" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>137287258</v>
       </c>
       <c r="B56" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92522</v>
+        <v>92534</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89392</v>
+        <v>89403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92534</v>
+        <v>92535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92535</v>
+        <v>92538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89404</v>
+        <v>89407</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 24281-2026 artfynd.xlsx
+++ b/artfynd/A 24281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137287294</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137287250</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137287290</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137287262</v>
       </c>
       <c r="B5" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137287271</v>
       </c>
       <c r="B6" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137287256</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137287266</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137287268</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137287276</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137287303</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137287274</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137287278</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137287279</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137287289</v>
       </c>
       <c r="B15" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137287273</v>
       </c>
       <c r="B16" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137287257</v>
       </c>
       <c r="B17" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137287297</v>
       </c>
       <c r="B18" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137287249</v>
       </c>
       <c r="B19" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137287240</v>
       </c>
       <c r="B20" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137287241</v>
       </c>
       <c r="B21" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137287244</v>
       </c>
       <c r="B22" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137287251</v>
       </c>
       <c r="B23" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137287252</v>
       </c>
       <c r="B24" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137287254</v>
       </c>
       <c r="B25" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137287285</v>
       </c>
       <c r="B26" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137287298</v>
       </c>
       <c r="B27" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137287260</v>
       </c>
       <c r="B28" t="n">
-        <v>92538</v>
+        <v>92542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>137287237</v>
       </c>
       <c r="B29" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>137287243</v>
       </c>
       <c r="B30" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>137287288</v>
       </c>
       <c r="B31" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>137287238</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137287264</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137287286</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>137287293</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>137287300</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>137287246</v>
       </c>
       <c r="B37" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137287269</v>
       </c>
       <c r="B38" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>137287270</v>
       </c>
       <c r="B39" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>137287283</v>
       </c>
       <c r="B40" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>137287292</v>
       </c>
       <c r="B41" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>137287255</v>
       </c>
       <c r="B42" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137287282</v>
       </c>
       <c r="B43" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>137287253</v>
       </c>
       <c r="B44" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>137287302</v>
       </c>
       <c r="B45" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137287284</v>
       </c>
       <c r="B46" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137287239</v>
       </c>
       <c r="B48" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>137287296</v>
       </c>
       <c r="B49" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>137287245</v>
       </c>
       <c r="B50" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>137287291</v>
       </c>
       <c r="B51" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>137287281</v>
       </c>
       <c r="B52" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>137287247</v>
       </c>
       <c r="B53" t="n">
-        <v>89407</v>
+        <v>89411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>137287275</v>
       </c>
       <c r="B54" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>137287295</v>
       </c>
       <c r="B55" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>137287258</v>
       </c>
       <c r="B56" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
